--- a/public/MAU_IMPORT_NHAN_VIEN.xlsx
+++ b/public/MAU_IMPORT_NHAN_VIEN.xlsx
@@ -402,11 +402,12 @@
             <sz val="10"/>
             <rFont val="Times New Roman"/>
           </rPr>
-          <t xml:space="preserve">• Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống.
+          <t xml:space="preserve">• Nhập 1; 2; 3; 4 (tách bằng dấu ;), hoặc để trống.
 • Ví dụ: 1; 3.
 1: lớp có % áp dụng 80%.
 2: chỉ Lớp kèm ONL áp dụng 80%.
-3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần.</t>
+3: IELTS - 56% ONL áp dụng 100%. 4: Lớp chung có % dùng 170.000đ/giờ. Ưu tiên 4 → 3 → 2/1.
+• Không giảm thêm 20%.</t>
         </r>
       </text>
     </comment>
@@ -882,11 +883,12 @@
             <sz val="10"/>
             <rFont val="Times New Roman"/>
           </rPr>
-          <t xml:space="preserve">• Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống.
+          <t xml:space="preserve">• Nhập 1; 2; 3; 4 (tách bằng dấu ;), hoặc để trống.
 • Ví dụ: 1; 3.
 1: lớp có % áp dụng 80%.
 2: chỉ Lớp kèm ONL áp dụng 80%.
-3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần.</t>
+3: IELTS - 56% ONL áp dụng 100%. 4: Lớp chung có % dùng 170.000đ/giờ. Ưu tiên 4 → 3 → 2/1.
+• Không giảm thêm 20%.</t>
         </r>
       </text>
     </comment>
@@ -1362,11 +1364,12 @@
             <sz val="10"/>
             <rFont val="Times New Roman"/>
           </rPr>
-          <t xml:space="preserve">• Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống.
+          <t xml:space="preserve">• Nhập 1; 2; 3; 4 (tách bằng dấu ;), hoặc để trống.
 • Ví dụ: 1; 3.
 1: lớp có % áp dụng 80%.
 2: chỉ Lớp kèm ONL áp dụng 80%.
-3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần.</t>
+3: IELTS - 56% ONL áp dụng 100%. 4: Lớp chung có % dùng 170.000đ/giờ. Ưu tiên 4 → 3 → 2/1.
+• Không giảm thêm 20%.</t>
         </r>
       </text>
     </comment>
@@ -2288,7 +2291,7 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Không cần chấm công" prompt="1 = Không cần chấm công; 0/trống = không bật." sqref="Q2:Q1000">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Cơ chế lương đặc biệt" prompt="Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống. Ví dụ: 1; 3. 1: lớp có % áp dụng 80%. 2: chỉ Lớp kèm ONL áp dụng 80%. 3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần." sqref="R2:R1000">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Cơ chế lương đặc biệt" prompt="Nhập 1; 2; 3; 4 (tách bằng dấu ;), hoặc để trống. Ví dụ: 1; 3. 1: lớp có % áp dụng 80%. 2: chỉ Lớp kèm ONL áp dụng 80%. 3: IELTS - 56% ONL áp dụng 100%. 4: Lớp chung có % dùng 170.000đ/giờ. Ưu tiên 4 → 3 → 2/1. Không giảm thêm 20%." sqref="R2:R1000">
       <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Email" prompt="Email của nhân viên. Có thể để trống." sqref="S2:S1000">

--- a/public/MAU_IMPORT_NHAN_VIEN.xlsx
+++ b/public/MAU_IMPORT_NHAN_VIEN.xlsx
@@ -439,11 +439,13 @@
             <sz val="10"/>
             <rFont val="Times New Roman"/>
           </rPr>
-          <t>• Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống.
-• Ví dụ: 1; 3.
-1: lớp có % áp dụng 80%.
-2: chỉ Lớp kèm ONL áp dụng 80%.
-3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần.</t>
+          <t xml:space="preserve">• Nhập mã 1, 2, 3 hoặc 4; nhiều mã tách bằng dấu ;. Để trống = không bật.
+• 1: Tên lớp có % → nhận 80% đơn giá tương ứng.
+• 2: Lớp kèm có ONL → nhận 80% đơn giá lớp kèm.
+• 3: IELTS - 56% ONL → giữ 100% đơn giá.
+• 4: Lớp chung có % → dùng 170.000đ/giờ.
+• Ưu tiên: 4/3 → 2/1; mỗi dòng chỉ áp dụng một cơ chế.
+• Chỉ chọn một trong cơ chế 3 hoặc 4; không bật cả hai.</t>
         </r>
       </text>
     </comment>
@@ -919,11 +921,13 @@
             <sz val="10"/>
             <rFont val="Times New Roman"/>
           </rPr>
-          <t>• Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống.
-• Ví dụ: 1; 3.
-1: lớp có % áp dụng 80%.
-2: chỉ Lớp kèm ONL áp dụng 80%.
-3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần.</t>
+          <t xml:space="preserve">• Nhập mã 1, 2, 3 hoặc 4; nhiều mã tách bằng dấu ;. Để trống = không bật.
+• 1: Tên lớp có % → nhận 80% đơn giá tương ứng.
+• 2: Lớp kèm có ONL → nhận 80% đơn giá lớp kèm.
+• 3: IELTS - 56% ONL → giữ 100% đơn giá.
+• 4: Lớp chung có % → dùng 170.000đ/giờ.
+• Ưu tiên: 4/3 → 2/1; mỗi dòng chỉ áp dụng một cơ chế.
+• Chỉ chọn một trong cơ chế 3 hoặc 4; không bật cả hai.</t>
         </r>
       </text>
     </comment>
@@ -1399,11 +1403,13 @@
             <sz val="10"/>
             <rFont val="Times New Roman"/>
           </rPr>
-          <t>• Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống.
-• Ví dụ: 1; 3.
-1: lớp có % áp dụng 80%.
-2: chỉ Lớp kèm ONL áp dụng 80%.
-3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần.</t>
+          <t xml:space="preserve">• Nhập mã 1, 2, 3 hoặc 4; nhiều mã tách bằng dấu ;. Để trống = không bật.
+• 1: Tên lớp có % → nhận 80% đơn giá tương ứng.
+• 2: Lớp kèm có ONL → nhận 80% đơn giá lớp kèm.
+• 3: IELTS - 56% ONL → giữ 100% đơn giá.
+• 4: Lớp chung có % → dùng 170.000đ/giờ.
+• Ưu tiên: 4/3 → 2/1; mỗi dòng chỉ áp dụng một cơ chế.
+• Chỉ chọn một trong cơ chế 3 hoặc 4; không bật cả hai.</t>
         </r>
       </text>
     </comment>

--- a/public/MAU_IMPORT_NHAN_VIEN.xlsx
+++ b/public/MAU_IMPORT_NHAN_VIEN.xlsx
@@ -3605,7 +3605,7 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Không cần chấm công" prompt="1 = Không cần chấm công; 0/trống = không bật." sqref="R2:R1037" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Cơ chế lương đặc biệt" prompt="Nhập 1; 2; 3 (tách bằng dấu ;), hoặc để trống. Ví dụ: 1; 3. 1: lớp có % áp dụng 80%. 2: chỉ Lớp kèm ONL áp dụng 80%. 3: IELTS - 56% ONL áp dụng 100%. Ưu tiên 3 → 2 → 1; không giảm hai lần." sqref="S2:S1037" xr:uid="{00000000-0002-0000-0000-000011000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Cơ chế lương đặc biệt" prompt="Nhập 1; 2; 3; 4 hoặc trống.&#10;1: Lớp có % → 80%.&#10;2: Lớp kèm ONL → 80%.&#10;3: IELTS - 56% ONL → 100%.&#10;4: Lớp chung có % → 170.000đ/giờ.&#10;Ưu tiên 4/3 → 2/1. Chỉ chọn 3 hoặc 4, không bật cả hai." sqref="S2:S1037" xr:uid="{00000000-0002-0000-0000-000011000000}">
       <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Ngày vào làm" prompt="Ngày vào làm: yyyy-mm-dd hoặc dd/mm/yyyy." sqref="T2:T1037" xr:uid="{00000000-0002-0000-0000-000013000000}">

--- a/public/MAU_IMPORT_NHAN_VIEN.xlsx
+++ b/public/MAU_IMPORT_NHAN_VIEN.xlsx
@@ -427,7 +427,6 @@
         <r>
           <rPr>
             <b/>
-            <color rgb="FF064E3B"/>
             <sz val="11"/>
             <rFont val="Times New Roman"/>
           </rPr>
@@ -439,8 +438,12 @@
             <sz val="10"/>
             <rFont val="Times New Roman"/>
           </rPr>
-          <t xml:space="preserve">• Để trống = không có dữ liệu.
-• Số 0 vẫn là có dữ liệu. </t>
+          <t xml:space="preserve">Nhập 1; 2; 3; 4, hoặc để trống.
+1: Chỉ lớp chung có % tính 80% đơn giá lớp chung. Không áp dụng cho phụ đạo, lớp kèm, phụ đạo kèm hoặc trợ giảng.
+2: Lớp kèm ONL tính 80%.
+3: IELTS - 56% ONL tính 100%.
+4: Lớp chung có % dùng 170.000đ/giờ.
+Chỉ chọn một trong 3 hoặc 4. Không giảm kép.</t>
         </r>
       </text>
     </comment>
@@ -3402,7 +3405,7 @@
       <c r="V40" s="10"/>
     </row>
   </sheetData>
-  <dataValidations count="52">
+  <dataValidations count="55">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Họ và tên" prompt="Tên đầy đủ, bắt buộc." sqref="A10:A1037">
       <formula1>TRUE</formula1>
     </dataValidation>
@@ -3550,10 +3553,19 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Đã nghỉ việc" prompt="1 = Đã nghỉ việc, chuyển vào mục Đã nghỉ việc. 0/trống = đang làm việc." sqref="V2:V1037">
       <formula1>TRUE</formula1>
     </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Chuyển khoản từ tài khoản công t" prompt="1 = dùng MS4/MS5 và xuất MS3 vào folder Chuyển khoản từ TK Công ty. 0/trống = không bật." sqref="W10:W1000">
+      <formula1>TRUE</formula1>
+    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Chuyển khoản từ tài khoản công t" prompt="1 = dùng MS4/MS5 và xuất MS3 vào folder Chuyển khoản từ TK Công ty. 0/trống = không bật." sqref="W2:W1000">
       <formula1>TRUE</formula1>
     </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Cơ chế tính bảo hiểm đặc biệt" prompt="1 = dùng trực tiếp số tiền BH đặc biệt nếu đã nhập, kể cả 0. 0/trống = dùng cơ chế BH thông thường." sqref="X10:X1000">
+      <formula1>TRUE</formula1>
+    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Cơ chế tính bảo hiểm đặc biệt" prompt="1 = dùng trực tiếp số tiền BH đặc biệt nếu đã nhập, kể cả 0. 0/trống = dùng cơ chế BH thông thường." sqref="X2:X1000">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Số tiền bảo hiểm đặc biệt" prompt="Số tiền BH trừ vào lương. Để trống: chưa nhập; nhập 0: không trừ BH. Công thức tính thuế và chuyển khoản sau BH giữ nguyên." sqref="Y10:Y1000">
       <formula1>TRUE</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="Số tiền bảo hiểm đặc biệt" prompt="Số tiền BH trừ vào lương. Để trống: chưa nhập; nhập 0: không trừ BH. Công thức tính thuế và chuyển khoản sau BH giữ nguyên." sqref="Y2:Y1000">
